--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="231">
   <si>
     <t>Execution Date</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 4:53:59 PM</t>
+    <t>6/15/2026, 5:27:13 PM</t>
   </si>
   <si>
     <t>Backend API Scanner</t>
@@ -92,13 +92,13 @@
     <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
   </si>
   <si>
-    <t>4:49:59 PM</t>
-  </si>
-  <si>
-    <t>4:50:02 PM</t>
-  </si>
-  <si>
-    <t>0.55s</t>
+    <t>5:23:13 PM</t>
+  </si>
+  <si>
+    <t>5:23:16 PM</t>
+  </si>
+  <si>
+    <t>0.84s</t>
   </si>
   <si>
     <t>TC_SEC_002</t>
@@ -107,13 +107,13 @@
     <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
   </si>
   <si>
-    <t>4:50:07 PM</t>
-  </si>
-  <si>
-    <t>4:50:10 PM</t>
-  </si>
-  <si>
-    <t>1.43s</t>
+    <t>5:23:21 PM</t>
+  </si>
+  <si>
+    <t>5:23:24 PM</t>
+  </si>
+  <si>
+    <t>0.61s</t>
   </si>
   <si>
     <t>TC_SEC_003</t>
@@ -122,13 +122,13 @@
     <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
   </si>
   <si>
-    <t>4:50:15 PM</t>
-  </si>
-  <si>
-    <t>4:50:18 PM</t>
-  </si>
-  <si>
-    <t>1.21s</t>
+    <t>5:23:29 PM</t>
+  </si>
+  <si>
+    <t>5:23:32 PM</t>
+  </si>
+  <si>
+    <t>1.50s</t>
   </si>
   <si>
     <t>TC_SEC_004</t>
@@ -140,13 +140,13 @@
     <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
   </si>
   <si>
-    <t>4:50:23 PM</t>
-  </si>
-  <si>
-    <t>4:50:26 PM</t>
-  </si>
-  <si>
-    <t>0.76s</t>
+    <t>5:23:37 PM</t>
+  </si>
+  <si>
+    <t>5:23:40 PM</t>
+  </si>
+  <si>
+    <t>1.60s</t>
   </si>
   <si>
     <t>TC_SEC_005</t>
@@ -155,13 +155,13 @@
     <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
   </si>
   <si>
-    <t>4:50:31 PM</t>
-  </si>
-  <si>
-    <t>4:50:34 PM</t>
-  </si>
-  <si>
-    <t>1.08s</t>
+    <t>5:23:45 PM</t>
+  </si>
+  <si>
+    <t>5:23:48 PM</t>
+  </si>
+  <si>
+    <t>1.93s</t>
   </si>
   <si>
     <t>TC_SEC_006</t>
@@ -170,13 +170,13 @@
     <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
   </si>
   <si>
-    <t>4:50:39 PM</t>
-  </si>
-  <si>
-    <t>4:50:42 PM</t>
-  </si>
-  <si>
-    <t>0.80s</t>
+    <t>5:23:53 PM</t>
+  </si>
+  <si>
+    <t>5:23:56 PM</t>
+  </si>
+  <si>
+    <t>1.97s</t>
   </si>
   <si>
     <t>TC_SEC_007</t>
@@ -185,13 +185,13 @@
     <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
   </si>
   <si>
-    <t>4:50:47 PM</t>
-  </si>
-  <si>
-    <t>4:50:50 PM</t>
-  </si>
-  <si>
-    <t>1.23s</t>
+    <t>5:24:01 PM</t>
+  </si>
+  <si>
+    <t>5:24:04 PM</t>
+  </si>
+  <si>
+    <t>1.86s</t>
   </si>
   <si>
     <t>TC_SEC_008</t>
@@ -203,13 +203,13 @@
     <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
   </si>
   <si>
-    <t>4:50:55 PM</t>
-  </si>
-  <si>
-    <t>4:50:58 PM</t>
-  </si>
-  <si>
-    <t>1.53s</t>
+    <t>5:24:09 PM</t>
+  </si>
+  <si>
+    <t>5:24:12 PM</t>
+  </si>
+  <si>
+    <t>1.63s</t>
   </si>
   <si>
     <t>TC_SEC_009</t>
@@ -218,13 +218,13 @@
     <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
   </si>
   <si>
-    <t>4:51:03 PM</t>
-  </si>
-  <si>
-    <t>4:51:06 PM</t>
-  </si>
-  <si>
-    <t>1.28s</t>
+    <t>5:24:17 PM</t>
+  </si>
+  <si>
+    <t>5:24:20 PM</t>
+  </si>
+  <si>
+    <t>1.90s</t>
   </si>
   <si>
     <t>TC_SEC_010</t>
@@ -233,163 +233,163 @@
     <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
   </si>
   <si>
-    <t>4:51:11 PM</t>
-  </si>
-  <si>
-    <t>4:51:14 PM</t>
+    <t>5:24:25 PM</t>
+  </si>
+  <si>
+    <t>5:24:28 PM</t>
+  </si>
+  <si>
+    <t>1.26s</t>
+  </si>
+  <si>
+    <t>TC_SEC_011</t>
+  </si>
+  <si>
+    <t>Access Control</t>
+  </si>
+  <si>
+    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
+  </si>
+  <si>
+    <t>5:24:33 PM</t>
+  </si>
+  <si>
+    <t>5:24:36 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_012</t>
+  </si>
+  <si>
+    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
+  </si>
+  <si>
+    <t>5:24:41 PM</t>
+  </si>
+  <si>
+    <t>5:24:44 PM</t>
+  </si>
+  <si>
+    <t>1.41s</t>
+  </si>
+  <si>
+    <t>TC_SEC_013</t>
+  </si>
+  <si>
+    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
+  </si>
+  <si>
+    <t>5:24:49 PM</t>
+  </si>
+  <si>
+    <t>5:24:52 PM</t>
+  </si>
+  <si>
+    <t>0.91s</t>
+  </si>
+  <si>
+    <t>TC_SEC_014</t>
+  </si>
+  <si>
+    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
+  </si>
+  <si>
+    <t>5:24:57 PM</t>
+  </si>
+  <si>
+    <t>5:25:00 PM</t>
+  </si>
+  <si>
+    <t>1.22s</t>
+  </si>
+  <si>
+    <t>TC_SEC_015</t>
+  </si>
+  <si>
+    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
+  </si>
+  <si>
+    <t>5:25:05 PM</t>
+  </si>
+  <si>
+    <t>5:25:08 PM</t>
+  </si>
+  <si>
+    <t>0.57s</t>
+  </si>
+  <si>
+    <t>TC_SEC_016</t>
+  </si>
+  <si>
+    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
+  </si>
+  <si>
+    <t>5:25:13 PM</t>
+  </si>
+  <si>
+    <t>5:25:16 PM</t>
+  </si>
+  <si>
+    <t>1.15s</t>
+  </si>
+  <si>
+    <t>TC_SEC_017</t>
+  </si>
+  <si>
+    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
+  </si>
+  <si>
+    <t>5:25:21 PM</t>
+  </si>
+  <si>
+    <t>5:25:24 PM</t>
+  </si>
+  <si>
+    <t>0.58s</t>
+  </si>
+  <si>
+    <t>TC_SEC_018</t>
+  </si>
+  <si>
+    <t>TC_SEC_018 - Verify file upload size validations</t>
+  </si>
+  <si>
+    <t>5:25:29 PM</t>
+  </si>
+  <si>
+    <t>5:25:32 PM</t>
+  </si>
+  <si>
+    <t>0.86s</t>
+  </si>
+  <si>
+    <t>TC_SEC_019</t>
+  </si>
+  <si>
+    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
+  </si>
+  <si>
+    <t>5:25:37 PM</t>
+  </si>
+  <si>
+    <t>5:25:40 PM</t>
   </si>
   <si>
     <t>1.95s</t>
   </si>
   <si>
-    <t>TC_SEC_011</t>
-  </si>
-  <si>
-    <t>Access Control</t>
-  </si>
-  <si>
-    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
-  </si>
-  <si>
-    <t>4:51:19 PM</t>
-  </si>
-  <si>
-    <t>4:51:22 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_012</t>
-  </si>
-  <si>
-    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
-  </si>
-  <si>
-    <t>4:51:27 PM</t>
-  </si>
-  <si>
-    <t>4:51:30 PM</t>
-  </si>
-  <si>
-    <t>0.81s</t>
-  </si>
-  <si>
-    <t>TC_SEC_013</t>
-  </si>
-  <si>
-    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
-  </si>
-  <si>
-    <t>4:51:35 PM</t>
-  </si>
-  <si>
-    <t>4:51:38 PM</t>
-  </si>
-  <si>
-    <t>1.06s</t>
-  </si>
-  <si>
-    <t>TC_SEC_014</t>
-  </si>
-  <si>
-    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
-  </si>
-  <si>
-    <t>4:51:43 PM</t>
-  </si>
-  <si>
-    <t>4:51:46 PM</t>
-  </si>
-  <si>
-    <t>1.14s</t>
-  </si>
-  <si>
-    <t>TC_SEC_015</t>
-  </si>
-  <si>
-    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
-  </si>
-  <si>
-    <t>4:51:51 PM</t>
-  </si>
-  <si>
-    <t>4:51:54 PM</t>
-  </si>
-  <si>
-    <t>1.50s</t>
-  </si>
-  <si>
-    <t>TC_SEC_016</t>
-  </si>
-  <si>
-    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
-  </si>
-  <si>
-    <t>4:51:59 PM</t>
-  </si>
-  <si>
-    <t>4:52:02 PM</t>
-  </si>
-  <si>
-    <t>1.92s</t>
-  </si>
-  <si>
-    <t>TC_SEC_017</t>
-  </si>
-  <si>
-    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
-  </si>
-  <si>
-    <t>4:52:07 PM</t>
-  </si>
-  <si>
-    <t>4:52:10 PM</t>
-  </si>
-  <si>
-    <t>1.67s</t>
-  </si>
-  <si>
-    <t>TC_SEC_018</t>
-  </si>
-  <si>
-    <t>TC_SEC_018 - Verify file upload size validations</t>
-  </si>
-  <si>
-    <t>4:52:15 PM</t>
-  </si>
-  <si>
-    <t>4:52:18 PM</t>
-  </si>
-  <si>
-    <t>0.87s</t>
-  </si>
-  <si>
-    <t>TC_SEC_019</t>
-  </si>
-  <si>
-    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
-  </si>
-  <si>
-    <t>4:52:23 PM</t>
-  </si>
-  <si>
-    <t>4:52:26 PM</t>
-  </si>
-  <si>
-    <t>1.05s</t>
-  </si>
-  <si>
     <t>TC_SEC_020</t>
   </si>
   <si>
     <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
   </si>
   <si>
-    <t>4:52:31 PM</t>
-  </si>
-  <si>
-    <t>4:52:34 PM</t>
-  </si>
-  <si>
-    <t>1.12s</t>
+    <t>5:25:45 PM</t>
+  </si>
+  <si>
+    <t>5:25:48 PM</t>
+  </si>
+  <si>
+    <t>1.36s</t>
   </si>
   <si>
     <t>TC_SEC_021</t>
@@ -401,13 +401,13 @@
     <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
   </si>
   <si>
-    <t>4:52:39 PM</t>
-  </si>
-  <si>
-    <t>4:52:42 PM</t>
-  </si>
-  <si>
-    <t>1.16s</t>
+    <t>5:25:53 PM</t>
+  </si>
+  <si>
+    <t>5:25:56 PM</t>
+  </si>
+  <si>
+    <t>1.79s</t>
   </si>
   <si>
     <t>TC_SEC_022</t>
@@ -416,13 +416,10 @@
     <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
   </si>
   <si>
-    <t>4:52:47 PM</t>
-  </si>
-  <si>
-    <t>4:52:50 PM</t>
-  </si>
-  <si>
-    <t>1.20s</t>
+    <t>5:26:01 PM</t>
+  </si>
+  <si>
+    <t>5:26:04 PM</t>
   </si>
   <si>
     <t>TC_SEC_023</t>
@@ -431,13 +428,13 @@
     <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
   </si>
   <si>
-    <t>4:52:55 PM</t>
-  </si>
-  <si>
-    <t>4:52:58 PM</t>
-  </si>
-  <si>
-    <t>1.38s</t>
+    <t>5:26:09 PM</t>
+  </si>
+  <si>
+    <t>5:26:12 PM</t>
+  </si>
+  <si>
+    <t>1.88s</t>
   </si>
   <si>
     <t>TC_SEC_024</t>
@@ -446,10 +443,10 @@
     <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
   </si>
   <si>
-    <t>4:53:03 PM</t>
-  </si>
-  <si>
-    <t>4:53:06 PM</t>
+    <t>5:26:17 PM</t>
+  </si>
+  <si>
+    <t>5:26:20 PM</t>
   </si>
   <si>
     <t>TC_SEC_025</t>
@@ -458,13 +455,13 @@
     <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
   </si>
   <si>
-    <t>4:53:11 PM</t>
-  </si>
-  <si>
-    <t>4:53:14 PM</t>
-  </si>
-  <si>
-    <t>1.88s</t>
+    <t>5:26:25 PM</t>
+  </si>
+  <si>
+    <t>5:26:28 PM</t>
+  </si>
+  <si>
+    <t>0.69s</t>
   </si>
   <si>
     <t>TC_SEC_026</t>
@@ -473,10 +470,10 @@
     <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
   </si>
   <si>
-    <t>4:53:19 PM</t>
-  </si>
-  <si>
-    <t>4:53:22 PM</t>
+    <t>5:26:33 PM</t>
+  </si>
+  <si>
+    <t>5:26:36 PM</t>
   </si>
   <si>
     <t>TC_SEC_027</t>
@@ -485,13 +482,13 @@
     <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
   </si>
   <si>
-    <t>4:53:27 PM</t>
-  </si>
-  <si>
-    <t>4:53:30 PM</t>
-  </si>
-  <si>
-    <t>1.47s</t>
+    <t>5:26:41 PM</t>
+  </si>
+  <si>
+    <t>5:26:44 PM</t>
+  </si>
+  <si>
+    <t>0.59s</t>
   </si>
   <si>
     <t>TC_SEC_028</t>
@@ -500,13 +497,10 @@
     <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
   </si>
   <si>
-    <t>4:53:35 PM</t>
-  </si>
-  <si>
-    <t>4:53:38 PM</t>
-  </si>
-  <si>
-    <t>0.62s</t>
+    <t>5:26:49 PM</t>
+  </si>
+  <si>
+    <t>5:26:52 PM</t>
   </si>
   <si>
     <t>TC_SEC_029</t>
@@ -515,13 +509,13 @@
     <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
   </si>
   <si>
-    <t>4:53:43 PM</t>
-  </si>
-  <si>
-    <t>4:53:46 PM</t>
-  </si>
-  <si>
-    <t>0.72s</t>
+    <t>5:26:57 PM</t>
+  </si>
+  <si>
+    <t>5:27:00 PM</t>
+  </si>
+  <si>
+    <t>1.07s</t>
   </si>
   <si>
     <t>TC_SEC_030</t>
@@ -530,10 +524,10 @@
     <t>TC_SEC_030 - Verify TLS version compliance checking</t>
   </si>
   <si>
-    <t>4:53:51 PM</t>
-  </si>
-  <si>
-    <t>4:53:54 PM</t>
+    <t>5:27:05 PM</t>
+  </si>
+  <si>
+    <t>5:27:08 PM</t>
   </si>
   <si>
     <t>8.50s</t>
@@ -572,7 +566,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T11:23:59.334Z</t>
+    <t>2026-06-15T11:57:13.606Z</t>
   </si>
   <si>
     <t>Execution of TC_SEC_001</t>
@@ -1553,7 +1547,7 @@
         <v>79</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1839,200 +1833,200 @@
         <v>134</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -2041,13 +2035,13 @@
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2071,13 +2065,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>17</v>
@@ -2086,18 +2080,18 @@
         <v>2</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>10</v>
@@ -2106,7 +2100,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2129,529 +2123,529 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>85</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>105</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>115</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>125</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>131</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2673,70 +2667,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="235">
   <si>
     <t>Execution Date</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:27:13 PM</t>
+    <t>6/15/2026, 5:34:55 PM</t>
   </si>
   <si>
     <t>Backend API Scanner</t>
@@ -92,13 +92,13 @@
     <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
   </si>
   <si>
-    <t>5:23:13 PM</t>
-  </si>
-  <si>
-    <t>5:23:16 PM</t>
-  </si>
-  <si>
-    <t>0.84s</t>
+    <t>5:30:55 PM</t>
+  </si>
+  <si>
+    <t>5:30:58 PM</t>
+  </si>
+  <si>
+    <t>1.59s</t>
   </si>
   <si>
     <t>TC_SEC_002</t>
@@ -107,13 +107,13 @@
     <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
   </si>
   <si>
-    <t>5:23:21 PM</t>
-  </si>
-  <si>
-    <t>5:23:24 PM</t>
-  </si>
-  <si>
-    <t>0.61s</t>
+    <t>5:31:03 PM</t>
+  </si>
+  <si>
+    <t>5:31:06 PM</t>
+  </si>
+  <si>
+    <t>0.94s</t>
   </si>
   <si>
     <t>TC_SEC_003</t>
@@ -122,385 +122,397 @@
     <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
   </si>
   <si>
-    <t>5:23:29 PM</t>
-  </si>
-  <si>
-    <t>5:23:32 PM</t>
+    <t>5:31:11 PM</t>
+  </si>
+  <si>
+    <t>5:31:14 PM</t>
+  </si>
+  <si>
+    <t>1.31s</t>
+  </si>
+  <si>
+    <t>TC_SEC_004</t>
+  </si>
+  <si>
+    <t>CSRF Prevention</t>
+  </si>
+  <si>
+    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
+  </si>
+  <si>
+    <t>5:31:19 PM</t>
+  </si>
+  <si>
+    <t>5:31:22 PM</t>
+  </si>
+  <si>
+    <t>1.67s</t>
+  </si>
+  <si>
+    <t>TC_SEC_005</t>
+  </si>
+  <si>
+    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
+  </si>
+  <si>
+    <t>5:31:27 PM</t>
+  </si>
+  <si>
+    <t>5:31:30 PM</t>
+  </si>
+  <si>
+    <t>1.97s</t>
+  </si>
+  <si>
+    <t>TC_SEC_006</t>
+  </si>
+  <si>
+    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
+  </si>
+  <si>
+    <t>5:31:35 PM</t>
+  </si>
+  <si>
+    <t>5:31:38 PM</t>
+  </si>
+  <si>
+    <t>1.27s</t>
+  </si>
+  <si>
+    <t>TC_SEC_007</t>
+  </si>
+  <si>
+    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
+  </si>
+  <si>
+    <t>5:31:43 PM</t>
+  </si>
+  <si>
+    <t>5:31:46 PM</t>
+  </si>
+  <si>
+    <t>1.01s</t>
+  </si>
+  <si>
+    <t>TC_SEC_008</t>
+  </si>
+  <si>
+    <t>JWT Validation</t>
+  </si>
+  <si>
+    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
+  </si>
+  <si>
+    <t>5:31:51 PM</t>
+  </si>
+  <si>
+    <t>5:31:54 PM</t>
+  </si>
+  <si>
+    <t>0.87s</t>
+  </si>
+  <si>
+    <t>TC_SEC_009</t>
+  </si>
+  <si>
+    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
+  </si>
+  <si>
+    <t>5:31:59 PM</t>
+  </si>
+  <si>
+    <t>5:32:02 PM</t>
+  </si>
+  <si>
+    <t>1.19s</t>
+  </si>
+  <si>
+    <t>TC_SEC_010</t>
+  </si>
+  <si>
+    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
+  </si>
+  <si>
+    <t>5:32:07 PM</t>
+  </si>
+  <si>
+    <t>5:32:10 PM</t>
+  </si>
+  <si>
+    <t>1.41s</t>
+  </si>
+  <si>
+    <t>TC_SEC_011</t>
+  </si>
+  <si>
+    <t>Access Control</t>
+  </si>
+  <si>
+    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
+  </si>
+  <si>
+    <t>5:32:15 PM</t>
+  </si>
+  <si>
+    <t>5:32:18 PM</t>
+  </si>
+  <si>
+    <t>1.73s</t>
+  </si>
+  <si>
+    <t>TC_SEC_012</t>
+  </si>
+  <si>
+    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
+  </si>
+  <si>
+    <t>5:32:23 PM</t>
+  </si>
+  <si>
+    <t>5:32:26 PM</t>
+  </si>
+  <si>
+    <t>1.53s</t>
+  </si>
+  <si>
+    <t>TC_SEC_013</t>
+  </si>
+  <si>
+    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
+  </si>
+  <si>
+    <t>5:32:31 PM</t>
+  </si>
+  <si>
+    <t>5:32:34 PM</t>
+  </si>
+  <si>
+    <t>0.82s</t>
+  </si>
+  <si>
+    <t>TC_SEC_014</t>
+  </si>
+  <si>
+    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
+  </si>
+  <si>
+    <t>5:32:39 PM</t>
+  </si>
+  <si>
+    <t>5:32:42 PM</t>
+  </si>
+  <si>
+    <t>1.29s</t>
+  </si>
+  <si>
+    <t>TC_SEC_015</t>
+  </si>
+  <si>
+    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
+  </si>
+  <si>
+    <t>5:32:47 PM</t>
+  </si>
+  <si>
+    <t>5:32:50 PM</t>
+  </si>
+  <si>
+    <t>1.99s</t>
+  </si>
+  <si>
+    <t>TC_SEC_016</t>
+  </si>
+  <si>
+    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
+  </si>
+  <si>
+    <t>5:32:55 PM</t>
+  </si>
+  <si>
+    <t>5:32:58 PM</t>
+  </si>
+  <si>
+    <t>1.79s</t>
+  </si>
+  <si>
+    <t>TC_SEC_017</t>
+  </si>
+  <si>
+    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
+  </si>
+  <si>
+    <t>5:33:03 PM</t>
+  </si>
+  <si>
+    <t>5:33:06 PM</t>
+  </si>
+  <si>
+    <t>1.72s</t>
+  </si>
+  <si>
+    <t>TC_SEC_018</t>
+  </si>
+  <si>
+    <t>TC_SEC_018 - Verify file upload size validations</t>
+  </si>
+  <si>
+    <t>5:33:11 PM</t>
+  </si>
+  <si>
+    <t>5:33:14 PM</t>
+  </si>
+  <si>
+    <t>0.74s</t>
+  </si>
+  <si>
+    <t>TC_SEC_019</t>
+  </si>
+  <si>
+    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
+  </si>
+  <si>
+    <t>5:33:19 PM</t>
+  </si>
+  <si>
+    <t>5:33:22 PM</t>
+  </si>
+  <si>
+    <t>0.55s</t>
+  </si>
+  <si>
+    <t>TC_SEC_020</t>
+  </si>
+  <si>
+    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
+  </si>
+  <si>
+    <t>5:33:27 PM</t>
+  </si>
+  <si>
+    <t>5:33:30 PM</t>
+  </si>
+  <si>
+    <t>0.59s</t>
+  </si>
+  <si>
+    <t>TC_SEC_021</t>
+  </si>
+  <si>
+    <t>HTTP Headers</t>
+  </si>
+  <si>
+    <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
+  </si>
+  <si>
+    <t>5:33:35 PM</t>
+  </si>
+  <si>
+    <t>5:33:38 PM</t>
+  </si>
+  <si>
+    <t>1.74s</t>
+  </si>
+  <si>
+    <t>TC_SEC_022</t>
+  </si>
+  <si>
+    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
+  </si>
+  <si>
+    <t>5:33:43 PM</t>
+  </si>
+  <si>
+    <t>5:33:46 PM</t>
+  </si>
+  <si>
+    <t>0.73s</t>
+  </si>
+  <si>
+    <t>TC_SEC_023</t>
+  </si>
+  <si>
+    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
+  </si>
+  <si>
+    <t>5:33:51 PM</t>
+  </si>
+  <si>
+    <t>5:33:54 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_024</t>
+  </si>
+  <si>
+    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
+  </si>
+  <si>
+    <t>5:33:59 PM</t>
+  </si>
+  <si>
+    <t>5:34:02 PM</t>
+  </si>
+  <si>
+    <t>1.81s</t>
+  </si>
+  <si>
+    <t>TC_SEC_025</t>
+  </si>
+  <si>
+    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
+  </si>
+  <si>
+    <t>5:34:07 PM</t>
+  </si>
+  <si>
+    <t>5:34:10 PM</t>
+  </si>
+  <si>
+    <t>1.52s</t>
+  </si>
+  <si>
+    <t>TC_SEC_026</t>
+  </si>
+  <si>
+    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
+  </si>
+  <si>
+    <t>5:34:15 PM</t>
+  </si>
+  <si>
+    <t>5:34:18 PM</t>
+  </si>
+  <si>
+    <t>0.69s</t>
+  </si>
+  <si>
+    <t>TC_SEC_027</t>
+  </si>
+  <si>
+    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
+  </si>
+  <si>
+    <t>5:34:23 PM</t>
+  </si>
+  <si>
+    <t>5:34:26 PM</t>
   </si>
   <si>
     <t>1.50s</t>
   </si>
   <si>
-    <t>TC_SEC_004</t>
-  </si>
-  <si>
-    <t>CSRF Prevention</t>
-  </si>
-  <si>
-    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
-  </si>
-  <si>
-    <t>5:23:37 PM</t>
-  </si>
-  <si>
-    <t>5:23:40 PM</t>
-  </si>
-  <si>
-    <t>1.60s</t>
-  </si>
-  <si>
-    <t>TC_SEC_005</t>
-  </si>
-  <si>
-    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
-  </si>
-  <si>
-    <t>5:23:45 PM</t>
-  </si>
-  <si>
-    <t>5:23:48 PM</t>
-  </si>
-  <si>
-    <t>1.93s</t>
-  </si>
-  <si>
-    <t>TC_SEC_006</t>
-  </si>
-  <si>
-    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
-  </si>
-  <si>
-    <t>5:23:53 PM</t>
-  </si>
-  <si>
-    <t>5:23:56 PM</t>
-  </si>
-  <si>
-    <t>1.97s</t>
-  </si>
-  <si>
-    <t>TC_SEC_007</t>
-  </si>
-  <si>
-    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
-  </si>
-  <si>
-    <t>5:24:01 PM</t>
-  </si>
-  <si>
-    <t>5:24:04 PM</t>
-  </si>
-  <si>
-    <t>1.86s</t>
-  </si>
-  <si>
-    <t>TC_SEC_008</t>
-  </si>
-  <si>
-    <t>JWT Validation</t>
-  </si>
-  <si>
-    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
-  </si>
-  <si>
-    <t>5:24:09 PM</t>
-  </si>
-  <si>
-    <t>5:24:12 PM</t>
-  </si>
-  <si>
-    <t>1.63s</t>
-  </si>
-  <si>
-    <t>TC_SEC_009</t>
-  </si>
-  <si>
-    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
-  </si>
-  <si>
-    <t>5:24:17 PM</t>
-  </si>
-  <si>
-    <t>5:24:20 PM</t>
-  </si>
-  <si>
-    <t>1.90s</t>
-  </si>
-  <si>
-    <t>TC_SEC_010</t>
-  </si>
-  <si>
-    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
-  </si>
-  <si>
-    <t>5:24:25 PM</t>
-  </si>
-  <si>
-    <t>5:24:28 PM</t>
-  </si>
-  <si>
-    <t>1.26s</t>
-  </si>
-  <si>
-    <t>TC_SEC_011</t>
-  </si>
-  <si>
-    <t>Access Control</t>
-  </si>
-  <si>
-    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
-  </si>
-  <si>
-    <t>5:24:33 PM</t>
-  </si>
-  <si>
-    <t>5:24:36 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_012</t>
-  </si>
-  <si>
-    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
-  </si>
-  <si>
-    <t>5:24:41 PM</t>
-  </si>
-  <si>
-    <t>5:24:44 PM</t>
-  </si>
-  <si>
-    <t>1.41s</t>
-  </si>
-  <si>
-    <t>TC_SEC_013</t>
-  </si>
-  <si>
-    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
-  </si>
-  <si>
-    <t>5:24:49 PM</t>
-  </si>
-  <si>
-    <t>5:24:52 PM</t>
-  </si>
-  <si>
-    <t>0.91s</t>
-  </si>
-  <si>
-    <t>TC_SEC_014</t>
-  </si>
-  <si>
-    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
-  </si>
-  <si>
-    <t>5:24:57 PM</t>
-  </si>
-  <si>
-    <t>5:25:00 PM</t>
-  </si>
-  <si>
-    <t>1.22s</t>
-  </si>
-  <si>
-    <t>TC_SEC_015</t>
-  </si>
-  <si>
-    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
-  </si>
-  <si>
-    <t>5:25:05 PM</t>
-  </si>
-  <si>
-    <t>5:25:08 PM</t>
-  </si>
-  <si>
-    <t>0.57s</t>
-  </si>
-  <si>
-    <t>TC_SEC_016</t>
-  </si>
-  <si>
-    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
-  </si>
-  <si>
-    <t>5:25:13 PM</t>
-  </si>
-  <si>
-    <t>5:25:16 PM</t>
-  </si>
-  <si>
-    <t>1.15s</t>
-  </si>
-  <si>
-    <t>TC_SEC_017</t>
-  </si>
-  <si>
-    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
-  </si>
-  <si>
-    <t>5:25:21 PM</t>
-  </si>
-  <si>
-    <t>5:25:24 PM</t>
-  </si>
-  <si>
-    <t>0.58s</t>
-  </si>
-  <si>
-    <t>TC_SEC_018</t>
-  </si>
-  <si>
-    <t>TC_SEC_018 - Verify file upload size validations</t>
-  </si>
-  <si>
-    <t>5:25:29 PM</t>
-  </si>
-  <si>
-    <t>5:25:32 PM</t>
-  </si>
-  <si>
-    <t>0.86s</t>
-  </si>
-  <si>
-    <t>TC_SEC_019</t>
-  </si>
-  <si>
-    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
-  </si>
-  <si>
-    <t>5:25:37 PM</t>
-  </si>
-  <si>
-    <t>5:25:40 PM</t>
-  </si>
-  <si>
-    <t>1.95s</t>
-  </si>
-  <si>
-    <t>TC_SEC_020</t>
-  </si>
-  <si>
-    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
-  </si>
-  <si>
-    <t>5:25:45 PM</t>
-  </si>
-  <si>
-    <t>5:25:48 PM</t>
-  </si>
-  <si>
-    <t>1.36s</t>
-  </si>
-  <si>
-    <t>TC_SEC_021</t>
-  </si>
-  <si>
-    <t>HTTP Headers</t>
-  </si>
-  <si>
-    <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
-  </si>
-  <si>
-    <t>5:25:53 PM</t>
-  </si>
-  <si>
-    <t>5:25:56 PM</t>
-  </si>
-  <si>
-    <t>1.79s</t>
-  </si>
-  <si>
-    <t>TC_SEC_022</t>
-  </si>
-  <si>
-    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
-  </si>
-  <si>
-    <t>5:26:01 PM</t>
-  </si>
-  <si>
-    <t>5:26:04 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_023</t>
-  </si>
-  <si>
-    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
-  </si>
-  <si>
-    <t>5:26:09 PM</t>
-  </si>
-  <si>
-    <t>5:26:12 PM</t>
-  </si>
-  <si>
-    <t>1.88s</t>
-  </si>
-  <si>
-    <t>TC_SEC_024</t>
-  </si>
-  <si>
-    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
-  </si>
-  <si>
-    <t>5:26:17 PM</t>
-  </si>
-  <si>
-    <t>5:26:20 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_025</t>
-  </si>
-  <si>
-    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
-  </si>
-  <si>
-    <t>5:26:25 PM</t>
-  </si>
-  <si>
-    <t>5:26:28 PM</t>
-  </si>
-  <si>
-    <t>0.69s</t>
-  </si>
-  <si>
-    <t>TC_SEC_026</t>
-  </si>
-  <si>
-    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
-  </si>
-  <si>
-    <t>5:26:33 PM</t>
-  </si>
-  <si>
-    <t>5:26:36 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_027</t>
-  </si>
-  <si>
-    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
-  </si>
-  <si>
-    <t>5:26:41 PM</t>
-  </si>
-  <si>
-    <t>5:26:44 PM</t>
-  </si>
-  <si>
-    <t>0.59s</t>
-  </si>
-  <si>
     <t>TC_SEC_028</t>
   </si>
   <si>
     <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
   </si>
   <si>
-    <t>5:26:49 PM</t>
-  </si>
-  <si>
-    <t>5:26:52 PM</t>
+    <t>5:34:31 PM</t>
+  </si>
+  <si>
+    <t>5:34:34 PM</t>
+  </si>
+  <si>
+    <t>1.02s</t>
   </si>
   <si>
     <t>TC_SEC_029</t>
@@ -509,13 +521,13 @@
     <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
   </si>
   <si>
-    <t>5:26:57 PM</t>
-  </si>
-  <si>
-    <t>5:27:00 PM</t>
-  </si>
-  <si>
-    <t>1.07s</t>
+    <t>5:34:39 PM</t>
+  </si>
+  <si>
+    <t>5:34:42 PM</t>
+  </si>
+  <si>
+    <t>0.80s</t>
   </si>
   <si>
     <t>TC_SEC_030</t>
@@ -524,10 +536,10 @@
     <t>TC_SEC_030 - Verify TLS version compliance checking</t>
   </si>
   <si>
-    <t>5:27:05 PM</t>
-  </si>
-  <si>
-    <t>5:27:08 PM</t>
+    <t>5:34:47 PM</t>
+  </si>
+  <si>
+    <t>5:34:50 PM</t>
   </si>
   <si>
     <t>8.50s</t>
@@ -566,7 +578,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T11:57:13.606Z</t>
+    <t>2026-06-15T12:04:55.278Z</t>
   </si>
   <si>
     <t>Execution of TC_SEC_001</t>
@@ -1547,18 +1559,18 @@
         <v>79</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -1567,24 +1579,24 @@
         <v>4</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1593,24 +1605,24 @@
         <v>4</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1619,24 +1631,24 @@
         <v>4</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1645,24 +1657,24 @@
         <v>4</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -1671,24 +1683,24 @@
         <v>4</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -1697,24 +1709,24 @@
         <v>4</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -1723,24 +1735,24 @@
         <v>4</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -1749,24 +1761,24 @@
         <v>4</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1775,24 +1787,24 @@
         <v>4</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1801,24 +1813,24 @@
         <v>4</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1827,24 +1839,24 @@
         <v>4</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -1853,24 +1865,24 @@
         <v>4</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1879,24 +1891,24 @@
         <v>4</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1905,24 +1917,24 @@
         <v>4</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -1931,24 +1943,24 @@
         <v>4</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>58</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
@@ -1957,24 +1969,24 @@
         <v>4</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
@@ -1983,24 +1995,24 @@
         <v>4</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -2009,24 +2021,24 @@
         <v>4</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -2035,13 +2047,13 @@
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2065,13 +2077,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>17</v>
@@ -2080,18 +2092,18 @@
         <v>2</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>10</v>
@@ -2100,7 +2112,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2123,529 +2135,529 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2667,70 +2679,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="270">
   <si>
     <t>Execution Date</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:34:55 PM</t>
+    <t>6/15/2026, 5:45:32 PM</t>
   </si>
   <si>
     <t>Backend API Scanner</t>
@@ -53,7 +53,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>96.67%</t>
+    <t>97.22%</t>
   </si>
   <si>
     <t>00:00:10</t>
@@ -92,309 +92,309 @@
     <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
   </si>
   <si>
-    <t>5:30:55 PM</t>
-  </si>
-  <si>
-    <t>5:30:58 PM</t>
+    <t>5:40:44 PM</t>
+  </si>
+  <si>
+    <t>5:40:47 PM</t>
+  </si>
+  <si>
+    <t>1.00s</t>
+  </si>
+  <si>
+    <t>TC_SEC_002</t>
+  </si>
+  <si>
+    <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
+  </si>
+  <si>
+    <t>5:40:52 PM</t>
+  </si>
+  <si>
+    <t>5:40:55 PM</t>
+  </si>
+  <si>
+    <t>1.96s</t>
+  </si>
+  <si>
+    <t>TC_SEC_003</t>
+  </si>
+  <si>
+    <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
+  </si>
+  <si>
+    <t>5:41:00 PM</t>
+  </si>
+  <si>
+    <t>5:41:03 PM</t>
+  </si>
+  <si>
+    <t>1.61s</t>
+  </si>
+  <si>
+    <t>TC_SEC_004</t>
+  </si>
+  <si>
+    <t>CSRF Prevention</t>
+  </si>
+  <si>
+    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
+  </si>
+  <si>
+    <t>5:41:08 PM</t>
+  </si>
+  <si>
+    <t>5:41:11 PM</t>
+  </si>
+  <si>
+    <t>1.11s</t>
+  </si>
+  <si>
+    <t>TC_SEC_005</t>
+  </si>
+  <si>
+    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
+  </si>
+  <si>
+    <t>5:41:16 PM</t>
+  </si>
+  <si>
+    <t>5:41:19 PM</t>
+  </si>
+  <si>
+    <t>0.82s</t>
+  </si>
+  <si>
+    <t>TC_SEC_006</t>
+  </si>
+  <si>
+    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
+  </si>
+  <si>
+    <t>5:41:24 PM</t>
+  </si>
+  <si>
+    <t>5:41:27 PM</t>
+  </si>
+  <si>
+    <t>1.55s</t>
+  </si>
+  <si>
+    <t>TC_SEC_007</t>
+  </si>
+  <si>
+    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
+  </si>
+  <si>
+    <t>5:41:32 PM</t>
+  </si>
+  <si>
+    <t>5:41:35 PM</t>
+  </si>
+  <si>
+    <t>1.82s</t>
+  </si>
+  <si>
+    <t>TC_SEC_008</t>
+  </si>
+  <si>
+    <t>JWT Validation</t>
+  </si>
+  <si>
+    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
+  </si>
+  <si>
+    <t>5:41:40 PM</t>
+  </si>
+  <si>
+    <t>5:41:43 PM</t>
+  </si>
+  <si>
+    <t>1.84s</t>
+  </si>
+  <si>
+    <t>TC_SEC_009</t>
+  </si>
+  <si>
+    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
+  </si>
+  <si>
+    <t>5:41:48 PM</t>
+  </si>
+  <si>
+    <t>5:41:51 PM</t>
+  </si>
+  <si>
+    <t>1.67s</t>
+  </si>
+  <si>
+    <t>TC_SEC_010</t>
+  </si>
+  <si>
+    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
+  </si>
+  <si>
+    <t>5:41:56 PM</t>
+  </si>
+  <si>
+    <t>5:41:59 PM</t>
+  </si>
+  <si>
+    <t>0.59s</t>
+  </si>
+  <si>
+    <t>TC_SEC_011</t>
+  </si>
+  <si>
+    <t>Access Control</t>
+  </si>
+  <si>
+    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
+  </si>
+  <si>
+    <t>5:42:04 PM</t>
+  </si>
+  <si>
+    <t>5:42:07 PM</t>
+  </si>
+  <si>
+    <t>1.69s</t>
+  </si>
+  <si>
+    <t>TC_SEC_012</t>
+  </si>
+  <si>
+    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
+  </si>
+  <si>
+    <t>5:42:12 PM</t>
+  </si>
+  <si>
+    <t>5:42:15 PM</t>
+  </si>
+  <si>
+    <t>0.71s</t>
+  </si>
+  <si>
+    <t>TC_SEC_013</t>
+  </si>
+  <si>
+    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
+  </si>
+  <si>
+    <t>5:42:20 PM</t>
+  </si>
+  <si>
+    <t>5:42:23 PM</t>
+  </si>
+  <si>
+    <t>0.53s</t>
+  </si>
+  <si>
+    <t>TC_SEC_014</t>
+  </si>
+  <si>
+    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
+  </si>
+  <si>
+    <t>5:42:28 PM</t>
+  </si>
+  <si>
+    <t>5:42:31 PM</t>
+  </si>
+  <si>
+    <t>0.69s</t>
+  </si>
+  <si>
+    <t>TC_SEC_015</t>
+  </si>
+  <si>
+    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
+  </si>
+  <si>
+    <t>5:42:36 PM</t>
+  </si>
+  <si>
+    <t>5:42:39 PM</t>
+  </si>
+  <si>
+    <t>1.71s</t>
+  </si>
+  <si>
+    <t>TC_SEC_016</t>
+  </si>
+  <si>
+    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
+  </si>
+  <si>
+    <t>5:42:44 PM</t>
+  </si>
+  <si>
+    <t>5:42:47 PM</t>
+  </si>
+  <si>
+    <t>0.70s</t>
+  </si>
+  <si>
+    <t>TC_SEC_017</t>
+  </si>
+  <si>
+    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
+  </si>
+  <si>
+    <t>5:42:52 PM</t>
+  </si>
+  <si>
+    <t>5:42:55 PM</t>
+  </si>
+  <si>
+    <t>1.14s</t>
+  </si>
+  <si>
+    <t>TC_SEC_018</t>
+  </si>
+  <si>
+    <t>TC_SEC_018 - Verify file upload size validations</t>
+  </si>
+  <si>
+    <t>5:43:00 PM</t>
+  </si>
+  <si>
+    <t>5:43:03 PM</t>
   </si>
   <si>
     <t>1.59s</t>
   </si>
   <si>
-    <t>TC_SEC_002</t>
-  </si>
-  <si>
-    <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
-  </si>
-  <si>
-    <t>5:31:03 PM</t>
-  </si>
-  <si>
-    <t>5:31:06 PM</t>
-  </si>
-  <si>
-    <t>0.94s</t>
-  </si>
-  <si>
-    <t>TC_SEC_003</t>
-  </si>
-  <si>
-    <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
-  </si>
-  <si>
-    <t>5:31:11 PM</t>
-  </si>
-  <si>
-    <t>5:31:14 PM</t>
-  </si>
-  <si>
-    <t>1.31s</t>
-  </si>
-  <si>
-    <t>TC_SEC_004</t>
-  </si>
-  <si>
-    <t>CSRF Prevention</t>
-  </si>
-  <si>
-    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
-  </si>
-  <si>
-    <t>5:31:19 PM</t>
-  </si>
-  <si>
-    <t>5:31:22 PM</t>
-  </si>
-  <si>
-    <t>1.67s</t>
-  </si>
-  <si>
-    <t>TC_SEC_005</t>
-  </si>
-  <si>
-    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
-  </si>
-  <si>
-    <t>5:31:27 PM</t>
-  </si>
-  <si>
-    <t>5:31:30 PM</t>
-  </si>
-  <si>
-    <t>1.97s</t>
-  </si>
-  <si>
-    <t>TC_SEC_006</t>
-  </si>
-  <si>
-    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
-  </si>
-  <si>
-    <t>5:31:35 PM</t>
-  </si>
-  <si>
-    <t>5:31:38 PM</t>
-  </si>
-  <si>
-    <t>1.27s</t>
-  </si>
-  <si>
-    <t>TC_SEC_007</t>
-  </si>
-  <si>
-    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
-  </si>
-  <si>
-    <t>5:31:43 PM</t>
-  </si>
-  <si>
-    <t>5:31:46 PM</t>
-  </si>
-  <si>
-    <t>1.01s</t>
-  </si>
-  <si>
-    <t>TC_SEC_008</t>
-  </si>
-  <si>
-    <t>JWT Validation</t>
-  </si>
-  <si>
-    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
-  </si>
-  <si>
-    <t>5:31:51 PM</t>
-  </si>
-  <si>
-    <t>5:31:54 PM</t>
-  </si>
-  <si>
-    <t>0.87s</t>
-  </si>
-  <si>
-    <t>TC_SEC_009</t>
-  </si>
-  <si>
-    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
-  </si>
-  <si>
-    <t>5:31:59 PM</t>
-  </si>
-  <si>
-    <t>5:32:02 PM</t>
-  </si>
-  <si>
-    <t>1.19s</t>
-  </si>
-  <si>
-    <t>TC_SEC_010</t>
-  </si>
-  <si>
-    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
-  </si>
-  <si>
-    <t>5:32:07 PM</t>
-  </si>
-  <si>
-    <t>5:32:10 PM</t>
-  </si>
-  <si>
-    <t>1.41s</t>
-  </si>
-  <si>
-    <t>TC_SEC_011</t>
-  </si>
-  <si>
-    <t>Access Control</t>
-  </si>
-  <si>
-    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
-  </si>
-  <si>
-    <t>5:32:15 PM</t>
-  </si>
-  <si>
-    <t>5:32:18 PM</t>
-  </si>
-  <si>
-    <t>1.73s</t>
-  </si>
-  <si>
-    <t>TC_SEC_012</t>
-  </si>
-  <si>
-    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
-  </si>
-  <si>
-    <t>5:32:23 PM</t>
-  </si>
-  <si>
-    <t>5:32:26 PM</t>
-  </si>
-  <si>
-    <t>1.53s</t>
-  </si>
-  <si>
-    <t>TC_SEC_013</t>
-  </si>
-  <si>
-    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
-  </si>
-  <si>
-    <t>5:32:31 PM</t>
-  </si>
-  <si>
-    <t>5:32:34 PM</t>
-  </si>
-  <si>
-    <t>0.82s</t>
-  </si>
-  <si>
-    <t>TC_SEC_014</t>
-  </si>
-  <si>
-    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
-  </si>
-  <si>
-    <t>5:32:39 PM</t>
-  </si>
-  <si>
-    <t>5:32:42 PM</t>
-  </si>
-  <si>
-    <t>1.29s</t>
-  </si>
-  <si>
-    <t>TC_SEC_015</t>
-  </si>
-  <si>
-    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
-  </si>
-  <si>
-    <t>5:32:47 PM</t>
-  </si>
-  <si>
-    <t>5:32:50 PM</t>
-  </si>
-  <si>
-    <t>1.99s</t>
-  </si>
-  <si>
-    <t>TC_SEC_016</t>
-  </si>
-  <si>
-    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
-  </si>
-  <si>
-    <t>5:32:55 PM</t>
-  </si>
-  <si>
-    <t>5:32:58 PM</t>
-  </si>
-  <si>
-    <t>1.79s</t>
-  </si>
-  <si>
-    <t>TC_SEC_017</t>
-  </si>
-  <si>
-    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
-  </si>
-  <si>
-    <t>5:33:03 PM</t>
-  </si>
-  <si>
-    <t>5:33:06 PM</t>
-  </si>
-  <si>
-    <t>1.72s</t>
-  </si>
-  <si>
-    <t>TC_SEC_018</t>
-  </si>
-  <si>
-    <t>TC_SEC_018 - Verify file upload size validations</t>
-  </si>
-  <si>
-    <t>5:33:11 PM</t>
-  </si>
-  <si>
-    <t>5:33:14 PM</t>
+    <t>TC_SEC_019</t>
+  </si>
+  <si>
+    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
+  </si>
+  <si>
+    <t>5:43:08 PM</t>
+  </si>
+  <si>
+    <t>5:43:11 PM</t>
+  </si>
+  <si>
+    <t>1.08s</t>
+  </si>
+  <si>
+    <t>TC_SEC_020</t>
+  </si>
+  <si>
+    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
+  </si>
+  <si>
+    <t>5:43:16 PM</t>
+  </si>
+  <si>
+    <t>5:43:19 PM</t>
   </si>
   <si>
     <t>0.74s</t>
   </si>
   <si>
-    <t>TC_SEC_019</t>
-  </si>
-  <si>
-    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
-  </si>
-  <si>
-    <t>5:33:19 PM</t>
-  </si>
-  <si>
-    <t>5:33:22 PM</t>
-  </si>
-  <si>
-    <t>0.55s</t>
-  </si>
-  <si>
-    <t>TC_SEC_020</t>
-  </si>
-  <si>
-    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
-  </si>
-  <si>
-    <t>5:33:27 PM</t>
-  </si>
-  <si>
-    <t>5:33:30 PM</t>
-  </si>
-  <si>
-    <t>0.59s</t>
-  </si>
-  <si>
     <t>TC_SEC_021</t>
   </si>
   <si>
@@ -404,147 +404,234 @@
     <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
   </si>
   <si>
-    <t>5:33:35 PM</t>
-  </si>
-  <si>
-    <t>5:33:38 PM</t>
+    <t>5:43:24 PM</t>
+  </si>
+  <si>
+    <t>5:43:27 PM</t>
+  </si>
+  <si>
+    <t>0.79s</t>
+  </si>
+  <si>
+    <t>TC_SEC_022</t>
+  </si>
+  <si>
+    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
+  </si>
+  <si>
+    <t>5:43:32 PM</t>
+  </si>
+  <si>
+    <t>5:43:35 PM</t>
+  </si>
+  <si>
+    <t>0.90s</t>
+  </si>
+  <si>
+    <t>TC_SEC_023</t>
+  </si>
+  <si>
+    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
+  </si>
+  <si>
+    <t>5:43:40 PM</t>
+  </si>
+  <si>
+    <t>5:43:43 PM</t>
+  </si>
+  <si>
+    <t>1.80s</t>
+  </si>
+  <si>
+    <t>TC_SEC_024</t>
+  </si>
+  <si>
+    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
+  </si>
+  <si>
+    <t>5:43:48 PM</t>
+  </si>
+  <si>
+    <t>5:43:51 PM</t>
+  </si>
+  <si>
+    <t>1.52s</t>
+  </si>
+  <si>
+    <t>TC_SEC_025</t>
+  </si>
+  <si>
+    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
+  </si>
+  <si>
+    <t>5:43:56 PM</t>
+  </si>
+  <si>
+    <t>5:43:59 PM</t>
+  </si>
+  <si>
+    <t>1.93s</t>
+  </si>
+  <si>
+    <t>TC_SEC_026</t>
+  </si>
+  <si>
+    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
+  </si>
+  <si>
+    <t>5:44:04 PM</t>
+  </si>
+  <si>
+    <t>5:44:07 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_027</t>
+  </si>
+  <si>
+    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
+  </si>
+  <si>
+    <t>5:44:12 PM</t>
+  </si>
+  <si>
+    <t>5:44:15 PM</t>
+  </si>
+  <si>
+    <t>1.68s</t>
+  </si>
+  <si>
+    <t>TC_SEC_028</t>
+  </si>
+  <si>
+    <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
+  </si>
+  <si>
+    <t>5:44:20 PM</t>
+  </si>
+  <si>
+    <t>5:44:23 PM</t>
+  </si>
+  <si>
+    <t>0.76s</t>
+  </si>
+  <si>
+    <t>TC_SEC_029</t>
+  </si>
+  <si>
+    <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
+  </si>
+  <si>
+    <t>5:44:28 PM</t>
+  </si>
+  <si>
+    <t>5:44:31 PM</t>
+  </si>
+  <si>
+    <t>1.09s</t>
+  </si>
+  <si>
+    <t>TC_SEC_030</t>
+  </si>
+  <si>
+    <t>TC_SEC_030 - Verify TLS version compliance checking</t>
+  </si>
+  <si>
+    <t>5:44:36 PM</t>
+  </si>
+  <si>
+    <t>5:44:39 PM</t>
+  </si>
+  <si>
+    <t>8.50s</t>
+  </si>
+  <si>
+    <t>TC_SEC_031</t>
+  </si>
+  <si>
+    <t>TC_SEC_031 - Verify API request rate limiting on forgot password</t>
+  </si>
+  <si>
+    <t>5:44:44 PM</t>
+  </si>
+  <si>
+    <t>5:44:47 PM</t>
+  </si>
+  <si>
+    <t>1.12s</t>
+  </si>
+  <si>
+    <t>TC_SEC_032</t>
+  </si>
+  <si>
+    <t>TC_SEC_032 - Verify secure header Referrer-Policy is set correctly</t>
+  </si>
+  <si>
+    <t>5:44:52 PM</t>
+  </si>
+  <si>
+    <t>5:44:55 PM</t>
+  </si>
+  <si>
+    <t>0.84s</t>
+  </si>
+  <si>
+    <t>TC_SEC_033</t>
+  </si>
+  <si>
+    <t>TC_SEC_033 - Verify session cookie path restricts access to domain</t>
+  </si>
+  <si>
+    <t>5:45:00 PM</t>
+  </si>
+  <si>
+    <t>5:45:03 PM</t>
+  </si>
+  <si>
+    <t>1.30s</t>
+  </si>
+  <si>
+    <t>TC_SEC_034</t>
+  </si>
+  <si>
+    <t>TC_SEC_034 - Verify brute force lockout mechanism on login</t>
+  </si>
+  <si>
+    <t>5:45:08 PM</t>
+  </si>
+  <si>
+    <t>5:45:11 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_035</t>
+  </si>
+  <si>
+    <t>TC_SEC_035 - Verify encryption of sensitive user payload at rest</t>
+  </si>
+  <si>
+    <t>5:45:16 PM</t>
+  </si>
+  <si>
+    <t>5:45:19 PM</t>
+  </si>
+  <si>
+    <t>1.91s</t>
+  </si>
+  <si>
+    <t>TC_SEC_036</t>
+  </si>
+  <si>
+    <t>TC_SEC_036 - Verify sanitization of file names on file system upload</t>
+  </si>
+  <si>
+    <t>5:45:24 PM</t>
+  </si>
+  <si>
+    <t>5:45:27 PM</t>
   </si>
   <si>
     <t>1.74s</t>
   </si>
   <si>
-    <t>TC_SEC_022</t>
-  </si>
-  <si>
-    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
-  </si>
-  <si>
-    <t>5:33:43 PM</t>
-  </si>
-  <si>
-    <t>5:33:46 PM</t>
-  </si>
-  <si>
-    <t>0.73s</t>
-  </si>
-  <si>
-    <t>TC_SEC_023</t>
-  </si>
-  <si>
-    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
-  </si>
-  <si>
-    <t>5:33:51 PM</t>
-  </si>
-  <si>
-    <t>5:33:54 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_024</t>
-  </si>
-  <si>
-    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
-  </si>
-  <si>
-    <t>5:33:59 PM</t>
-  </si>
-  <si>
-    <t>5:34:02 PM</t>
-  </si>
-  <si>
-    <t>1.81s</t>
-  </si>
-  <si>
-    <t>TC_SEC_025</t>
-  </si>
-  <si>
-    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
-  </si>
-  <si>
-    <t>5:34:07 PM</t>
-  </si>
-  <si>
-    <t>5:34:10 PM</t>
-  </si>
-  <si>
-    <t>1.52s</t>
-  </si>
-  <si>
-    <t>TC_SEC_026</t>
-  </si>
-  <si>
-    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
-  </si>
-  <si>
-    <t>5:34:15 PM</t>
-  </si>
-  <si>
-    <t>5:34:18 PM</t>
-  </si>
-  <si>
-    <t>0.69s</t>
-  </si>
-  <si>
-    <t>TC_SEC_027</t>
-  </si>
-  <si>
-    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
-  </si>
-  <si>
-    <t>5:34:23 PM</t>
-  </si>
-  <si>
-    <t>5:34:26 PM</t>
-  </si>
-  <si>
-    <t>1.50s</t>
-  </si>
-  <si>
-    <t>TC_SEC_028</t>
-  </si>
-  <si>
-    <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
-  </si>
-  <si>
-    <t>5:34:31 PM</t>
-  </si>
-  <si>
-    <t>5:34:34 PM</t>
-  </si>
-  <si>
-    <t>1.02s</t>
-  </si>
-  <si>
-    <t>TC_SEC_029</t>
-  </si>
-  <si>
-    <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
-  </si>
-  <si>
-    <t>5:34:39 PM</t>
-  </si>
-  <si>
-    <t>5:34:42 PM</t>
-  </si>
-  <si>
-    <t>0.80s</t>
-  </si>
-  <si>
-    <t>TC_SEC_030</t>
-  </si>
-  <si>
-    <t>TC_SEC_030 - Verify TLS version compliance checking</t>
-  </si>
-  <si>
-    <t>5:34:47 PM</t>
-  </si>
-  <si>
-    <t>5:34:50 PM</t>
-  </si>
-  <si>
-    <t>8.50s</t>
-  </si>
-  <si>
     <t>Test Name</t>
   </si>
   <si>
@@ -578,7 +665,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T12:04:55.278Z</t>
+    <t>2026-06-15T12:15:32.241Z</t>
   </si>
   <si>
     <t>Execution of TC_SEC_001</t>
@@ -681,6 +768,24 @@
   </si>
   <si>
     <t>Audit found TLS 1.0 support enabled on test server endpoint</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEC_031</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEC_032</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEC_033</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEC_034</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEC_035</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEC_036</t>
   </si>
   <si>
     <t>Metric Name</t>
@@ -1212,10 +1317,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -1238,7 +1343,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1871,18 +1976,18 @@
         <v>140</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1891,24 +1996,24 @@
         <v>4</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1917,24 +2022,24 @@
         <v>4</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -1943,13 +2048,13 @@
         <v>4</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>155</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -2054,6 +2159,162 @@
       </c>
       <c r="H31" s="2" t="s">
         <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2077,13 +2338,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>17</v>
@@ -2092,7 +2353,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2100,10 +2361,10 @@
         <v>172</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>10</v>
@@ -2112,7 +2373,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -2123,7 +2384,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -2135,529 +2396,631 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>106</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>121</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>137</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>156</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>161</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>166</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>171</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>221</v>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2679,70 +3042,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>226</v>
+        <v>261</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="269">
   <si>
     <t>Execution Date</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:45:32 PM</t>
+    <t>6/15/2026, 6:07:07 PM</t>
   </si>
   <si>
     <t>Backend API Scanner</t>
@@ -92,13 +92,13 @@
     <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
   </si>
   <si>
-    <t>5:40:44 PM</t>
-  </si>
-  <si>
-    <t>5:40:47 PM</t>
-  </si>
-  <si>
-    <t>1.00s</t>
+    <t>6:02:19 PM</t>
+  </si>
+  <si>
+    <t>6:02:22 PM</t>
+  </si>
+  <si>
+    <t>1.85s</t>
   </si>
   <si>
     <t>TC_SEC_002</t>
@@ -107,13 +107,13 @@
     <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
   </si>
   <si>
-    <t>5:40:52 PM</t>
-  </si>
-  <si>
-    <t>5:40:55 PM</t>
-  </si>
-  <si>
-    <t>1.96s</t>
+    <t>6:02:27 PM</t>
+  </si>
+  <si>
+    <t>6:02:30 PM</t>
+  </si>
+  <si>
+    <t>0.53s</t>
   </si>
   <si>
     <t>TC_SEC_003</t>
@@ -122,13 +122,13 @@
     <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
   </si>
   <si>
-    <t>5:41:00 PM</t>
-  </si>
-  <si>
-    <t>5:41:03 PM</t>
-  </si>
-  <si>
-    <t>1.61s</t>
+    <t>6:02:35 PM</t>
+  </si>
+  <si>
+    <t>6:02:38 PM</t>
+  </si>
+  <si>
+    <t>1.72s</t>
   </si>
   <si>
     <t>TC_SEC_004</t>
@@ -140,13 +140,13 @@
     <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
   </si>
   <si>
-    <t>5:41:08 PM</t>
-  </si>
-  <si>
-    <t>5:41:11 PM</t>
-  </si>
-  <si>
-    <t>1.11s</t>
+    <t>6:02:43 PM</t>
+  </si>
+  <si>
+    <t>6:02:46 PM</t>
+  </si>
+  <si>
+    <t>1.64s</t>
   </si>
   <si>
     <t>TC_SEC_005</t>
@@ -155,13 +155,13 @@
     <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
   </si>
   <si>
-    <t>5:41:16 PM</t>
-  </si>
-  <si>
-    <t>5:41:19 PM</t>
-  </si>
-  <si>
-    <t>0.82s</t>
+    <t>6:02:51 PM</t>
+  </si>
+  <si>
+    <t>6:02:54 PM</t>
+  </si>
+  <si>
+    <t>0.67s</t>
   </si>
   <si>
     <t>TC_SEC_006</t>
@@ -170,13 +170,13 @@
     <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
   </si>
   <si>
-    <t>5:41:24 PM</t>
-  </si>
-  <si>
-    <t>5:41:27 PM</t>
-  </si>
-  <si>
-    <t>1.55s</t>
+    <t>6:02:59 PM</t>
+  </si>
+  <si>
+    <t>6:03:02 PM</t>
+  </si>
+  <si>
+    <t>0.70s</t>
   </si>
   <si>
     <t>TC_SEC_007</t>
@@ -185,451 +185,448 @@
     <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
   </si>
   <si>
-    <t>5:41:32 PM</t>
-  </si>
-  <si>
-    <t>5:41:35 PM</t>
+    <t>6:03:07 PM</t>
+  </si>
+  <si>
+    <t>6:03:10 PM</t>
+  </si>
+  <si>
+    <t>1.93s</t>
+  </si>
+  <si>
+    <t>TC_SEC_008</t>
+  </si>
+  <si>
+    <t>JWT Validation</t>
+  </si>
+  <si>
+    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
+  </si>
+  <si>
+    <t>6:03:15 PM</t>
+  </si>
+  <si>
+    <t>6:03:18 PM</t>
+  </si>
+  <si>
+    <t>0.61s</t>
+  </si>
+  <si>
+    <t>TC_SEC_009</t>
+  </si>
+  <si>
+    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
+  </si>
+  <si>
+    <t>6:03:23 PM</t>
+  </si>
+  <si>
+    <t>6:03:26 PM</t>
+  </si>
+  <si>
+    <t>1.29s</t>
+  </si>
+  <si>
+    <t>TC_SEC_010</t>
+  </si>
+  <si>
+    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
+  </si>
+  <si>
+    <t>6:03:31 PM</t>
+  </si>
+  <si>
+    <t>6:03:34 PM</t>
+  </si>
+  <si>
+    <t>1.54s</t>
+  </si>
+  <si>
+    <t>TC_SEC_011</t>
+  </si>
+  <si>
+    <t>Access Control</t>
+  </si>
+  <si>
+    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
+  </si>
+  <si>
+    <t>6:03:39 PM</t>
+  </si>
+  <si>
+    <t>6:03:42 PM</t>
+  </si>
+  <si>
+    <t>0.74s</t>
+  </si>
+  <si>
+    <t>TC_SEC_012</t>
+  </si>
+  <si>
+    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
+  </si>
+  <si>
+    <t>6:03:47 PM</t>
+  </si>
+  <si>
+    <t>6:03:50 PM</t>
+  </si>
+  <si>
+    <t>1.35s</t>
+  </si>
+  <si>
+    <t>TC_SEC_013</t>
+  </si>
+  <si>
+    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
+  </si>
+  <si>
+    <t>6:03:55 PM</t>
+  </si>
+  <si>
+    <t>6:03:58 PM</t>
+  </si>
+  <si>
+    <t>1.90s</t>
+  </si>
+  <si>
+    <t>TC_SEC_014</t>
+  </si>
+  <si>
+    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
+  </si>
+  <si>
+    <t>6:04:03 PM</t>
+  </si>
+  <si>
+    <t>6:04:06 PM</t>
+  </si>
+  <si>
+    <t>1.69s</t>
+  </si>
+  <si>
+    <t>TC_SEC_015</t>
+  </si>
+  <si>
+    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
+  </si>
+  <si>
+    <t>6:04:11 PM</t>
+  </si>
+  <si>
+    <t>6:04:14 PM</t>
+  </si>
+  <si>
+    <t>1.99s</t>
+  </si>
+  <si>
+    <t>TC_SEC_016</t>
+  </si>
+  <si>
+    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
+  </si>
+  <si>
+    <t>6:04:19 PM</t>
+  </si>
+  <si>
+    <t>6:04:22 PM</t>
+  </si>
+  <si>
+    <t>0.60s</t>
+  </si>
+  <si>
+    <t>TC_SEC_017</t>
+  </si>
+  <si>
+    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
+  </si>
+  <si>
+    <t>6:04:27 PM</t>
+  </si>
+  <si>
+    <t>6:04:30 PM</t>
+  </si>
+  <si>
+    <t>0.84s</t>
+  </si>
+  <si>
+    <t>TC_SEC_018</t>
+  </si>
+  <si>
+    <t>TC_SEC_018 - Verify file upload size validations</t>
+  </si>
+  <si>
+    <t>6:04:35 PM</t>
+  </si>
+  <si>
+    <t>6:04:38 PM</t>
+  </si>
+  <si>
+    <t>0.97s</t>
+  </si>
+  <si>
+    <t>TC_SEC_019</t>
+  </si>
+  <si>
+    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
+  </si>
+  <si>
+    <t>6:04:43 PM</t>
+  </si>
+  <si>
+    <t>6:04:46 PM</t>
+  </si>
+  <si>
+    <t>1.31s</t>
+  </si>
+  <si>
+    <t>TC_SEC_020</t>
+  </si>
+  <si>
+    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
+  </si>
+  <si>
+    <t>6:04:51 PM</t>
+  </si>
+  <si>
+    <t>6:04:54 PM</t>
+  </si>
+  <si>
+    <t>0.79s</t>
+  </si>
+  <si>
+    <t>TC_SEC_021</t>
+  </si>
+  <si>
+    <t>HTTP Headers</t>
+  </si>
+  <si>
+    <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
+  </si>
+  <si>
+    <t>6:04:59 PM</t>
+  </si>
+  <si>
+    <t>6:05:02 PM</t>
+  </si>
+  <si>
+    <t>1.13s</t>
+  </si>
+  <si>
+    <t>TC_SEC_022</t>
+  </si>
+  <si>
+    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
+  </si>
+  <si>
+    <t>6:05:07 PM</t>
+  </si>
+  <si>
+    <t>6:05:10 PM</t>
+  </si>
+  <si>
+    <t>1.27s</t>
+  </si>
+  <si>
+    <t>TC_SEC_023</t>
+  </si>
+  <si>
+    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
+  </si>
+  <si>
+    <t>6:05:15 PM</t>
+  </si>
+  <si>
+    <t>6:05:18 PM</t>
+  </si>
+  <si>
+    <t>1.57s</t>
+  </si>
+  <si>
+    <t>TC_SEC_024</t>
+  </si>
+  <si>
+    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
+  </si>
+  <si>
+    <t>6:05:23 PM</t>
+  </si>
+  <si>
+    <t>6:05:26 PM</t>
+  </si>
+  <si>
+    <t>1.43s</t>
+  </si>
+  <si>
+    <t>TC_SEC_025</t>
+  </si>
+  <si>
+    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
+  </si>
+  <si>
+    <t>6:05:31 PM</t>
+  </si>
+  <si>
+    <t>6:05:34 PM</t>
+  </si>
+  <si>
+    <t>0.92s</t>
+  </si>
+  <si>
+    <t>TC_SEC_026</t>
+  </si>
+  <si>
+    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
+  </si>
+  <si>
+    <t>6:05:39 PM</t>
+  </si>
+  <si>
+    <t>6:05:42 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_027</t>
+  </si>
+  <si>
+    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
+  </si>
+  <si>
+    <t>6:05:47 PM</t>
+  </si>
+  <si>
+    <t>6:05:50 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_028</t>
+  </si>
+  <si>
+    <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
+  </si>
+  <si>
+    <t>6:05:55 PM</t>
+  </si>
+  <si>
+    <t>6:05:58 PM</t>
+  </si>
+  <si>
+    <t>1.42s</t>
+  </si>
+  <si>
+    <t>TC_SEC_029</t>
+  </si>
+  <si>
+    <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
+  </si>
+  <si>
+    <t>6:06:03 PM</t>
+  </si>
+  <si>
+    <t>6:06:06 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_030</t>
+  </si>
+  <si>
+    <t>TC_SEC_030 - Verify TLS version compliance checking</t>
+  </si>
+  <si>
+    <t>6:06:11 PM</t>
+  </si>
+  <si>
+    <t>6:06:14 PM</t>
+  </si>
+  <si>
+    <t>8.50s</t>
+  </si>
+  <si>
+    <t>TC_SEC_031</t>
+  </si>
+  <si>
+    <t>TC_SEC_031 - Verify API request rate limiting on forgot password</t>
+  </si>
+  <si>
+    <t>6:06:19 PM</t>
+  </si>
+  <si>
+    <t>6:06:22 PM</t>
+  </si>
+  <si>
+    <t>0.85s</t>
+  </si>
+  <si>
+    <t>TC_SEC_032</t>
+  </si>
+  <si>
+    <t>TC_SEC_032 - Verify secure header Referrer-Policy is set correctly</t>
+  </si>
+  <si>
+    <t>6:06:27 PM</t>
+  </si>
+  <si>
+    <t>6:06:30 PM</t>
+  </si>
+  <si>
+    <t>1.53s</t>
+  </si>
+  <si>
+    <t>TC_SEC_033</t>
+  </si>
+  <si>
+    <t>TC_SEC_033 - Verify session cookie path restricts access to domain</t>
+  </si>
+  <si>
+    <t>6:06:35 PM</t>
+  </si>
+  <si>
+    <t>6:06:38 PM</t>
+  </si>
+  <si>
+    <t>1.81s</t>
+  </si>
+  <si>
+    <t>TC_SEC_034</t>
+  </si>
+  <si>
+    <t>TC_SEC_034 - Verify brute force lockout mechanism on login</t>
+  </si>
+  <si>
+    <t>6:06:43 PM</t>
+  </si>
+  <si>
+    <t>6:06:46 PM</t>
+  </si>
+  <si>
+    <t>1.48s</t>
+  </si>
+  <si>
+    <t>TC_SEC_035</t>
+  </si>
+  <si>
+    <t>TC_SEC_035 - Verify encryption of sensitive user payload at rest</t>
+  </si>
+  <si>
+    <t>6:06:51 PM</t>
+  </si>
+  <si>
+    <t>6:06:54 PM</t>
   </si>
   <si>
     <t>1.82s</t>
   </si>
   <si>
-    <t>TC_SEC_008</t>
-  </si>
-  <si>
-    <t>JWT Validation</t>
-  </si>
-  <si>
-    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
-  </si>
-  <si>
-    <t>5:41:40 PM</t>
-  </si>
-  <si>
-    <t>5:41:43 PM</t>
-  </si>
-  <si>
-    <t>1.84s</t>
-  </si>
-  <si>
-    <t>TC_SEC_009</t>
-  </si>
-  <si>
-    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
-  </si>
-  <si>
-    <t>5:41:48 PM</t>
-  </si>
-  <si>
-    <t>5:41:51 PM</t>
-  </si>
-  <si>
-    <t>1.67s</t>
-  </si>
-  <si>
-    <t>TC_SEC_010</t>
-  </si>
-  <si>
-    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
-  </si>
-  <si>
-    <t>5:41:56 PM</t>
-  </si>
-  <si>
-    <t>5:41:59 PM</t>
-  </si>
-  <si>
-    <t>0.59s</t>
-  </si>
-  <si>
-    <t>TC_SEC_011</t>
-  </si>
-  <si>
-    <t>Access Control</t>
-  </si>
-  <si>
-    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
-  </si>
-  <si>
-    <t>5:42:04 PM</t>
-  </si>
-  <si>
-    <t>5:42:07 PM</t>
-  </si>
-  <si>
-    <t>1.69s</t>
-  </si>
-  <si>
-    <t>TC_SEC_012</t>
-  </si>
-  <si>
-    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
-  </si>
-  <si>
-    <t>5:42:12 PM</t>
-  </si>
-  <si>
-    <t>5:42:15 PM</t>
-  </si>
-  <si>
-    <t>0.71s</t>
-  </si>
-  <si>
-    <t>TC_SEC_013</t>
-  </si>
-  <si>
-    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
-  </si>
-  <si>
-    <t>5:42:20 PM</t>
-  </si>
-  <si>
-    <t>5:42:23 PM</t>
-  </si>
-  <si>
-    <t>0.53s</t>
-  </si>
-  <si>
-    <t>TC_SEC_014</t>
-  </si>
-  <si>
-    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
-  </si>
-  <si>
-    <t>5:42:28 PM</t>
-  </si>
-  <si>
-    <t>5:42:31 PM</t>
-  </si>
-  <si>
-    <t>0.69s</t>
-  </si>
-  <si>
-    <t>TC_SEC_015</t>
-  </si>
-  <si>
-    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
-  </si>
-  <si>
-    <t>5:42:36 PM</t>
-  </si>
-  <si>
-    <t>5:42:39 PM</t>
-  </si>
-  <si>
-    <t>1.71s</t>
-  </si>
-  <si>
-    <t>TC_SEC_016</t>
-  </si>
-  <si>
-    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
-  </si>
-  <si>
-    <t>5:42:44 PM</t>
-  </si>
-  <si>
-    <t>5:42:47 PM</t>
-  </si>
-  <si>
-    <t>0.70s</t>
-  </si>
-  <si>
-    <t>TC_SEC_017</t>
-  </si>
-  <si>
-    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
-  </si>
-  <si>
-    <t>5:42:52 PM</t>
-  </si>
-  <si>
-    <t>5:42:55 PM</t>
-  </si>
-  <si>
-    <t>1.14s</t>
-  </si>
-  <si>
-    <t>TC_SEC_018</t>
-  </si>
-  <si>
-    <t>TC_SEC_018 - Verify file upload size validations</t>
-  </si>
-  <si>
-    <t>5:43:00 PM</t>
-  </si>
-  <si>
-    <t>5:43:03 PM</t>
-  </si>
-  <si>
-    <t>1.59s</t>
-  </si>
-  <si>
-    <t>TC_SEC_019</t>
-  </si>
-  <si>
-    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
-  </si>
-  <si>
-    <t>5:43:08 PM</t>
-  </si>
-  <si>
-    <t>5:43:11 PM</t>
-  </si>
-  <si>
-    <t>1.08s</t>
-  </si>
-  <si>
-    <t>TC_SEC_020</t>
-  </si>
-  <si>
-    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
-  </si>
-  <si>
-    <t>5:43:16 PM</t>
-  </si>
-  <si>
-    <t>5:43:19 PM</t>
-  </si>
-  <si>
-    <t>0.74s</t>
-  </si>
-  <si>
-    <t>TC_SEC_021</t>
-  </si>
-  <si>
-    <t>HTTP Headers</t>
-  </si>
-  <si>
-    <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
-  </si>
-  <si>
-    <t>5:43:24 PM</t>
-  </si>
-  <si>
-    <t>5:43:27 PM</t>
-  </si>
-  <si>
-    <t>0.79s</t>
-  </si>
-  <si>
-    <t>TC_SEC_022</t>
-  </si>
-  <si>
-    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
-  </si>
-  <si>
-    <t>5:43:32 PM</t>
-  </si>
-  <si>
-    <t>5:43:35 PM</t>
-  </si>
-  <si>
-    <t>0.90s</t>
-  </si>
-  <si>
-    <t>TC_SEC_023</t>
-  </si>
-  <si>
-    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
-  </si>
-  <si>
-    <t>5:43:40 PM</t>
-  </si>
-  <si>
-    <t>5:43:43 PM</t>
-  </si>
-  <si>
-    <t>1.80s</t>
-  </si>
-  <si>
-    <t>TC_SEC_024</t>
-  </si>
-  <si>
-    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
-  </si>
-  <si>
-    <t>5:43:48 PM</t>
-  </si>
-  <si>
-    <t>5:43:51 PM</t>
-  </si>
-  <si>
-    <t>1.52s</t>
-  </si>
-  <si>
-    <t>TC_SEC_025</t>
-  </si>
-  <si>
-    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
-  </si>
-  <si>
-    <t>5:43:56 PM</t>
-  </si>
-  <si>
-    <t>5:43:59 PM</t>
-  </si>
-  <si>
-    <t>1.93s</t>
-  </si>
-  <si>
-    <t>TC_SEC_026</t>
-  </si>
-  <si>
-    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
-  </si>
-  <si>
-    <t>5:44:04 PM</t>
-  </si>
-  <si>
-    <t>5:44:07 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_027</t>
-  </si>
-  <si>
-    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
-  </si>
-  <si>
-    <t>5:44:12 PM</t>
-  </si>
-  <si>
-    <t>5:44:15 PM</t>
-  </si>
-  <si>
-    <t>1.68s</t>
-  </si>
-  <si>
-    <t>TC_SEC_028</t>
-  </si>
-  <si>
-    <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
-  </si>
-  <si>
-    <t>5:44:20 PM</t>
-  </si>
-  <si>
-    <t>5:44:23 PM</t>
-  </si>
-  <si>
-    <t>0.76s</t>
-  </si>
-  <si>
-    <t>TC_SEC_029</t>
-  </si>
-  <si>
-    <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
-  </si>
-  <si>
-    <t>5:44:28 PM</t>
-  </si>
-  <si>
-    <t>5:44:31 PM</t>
-  </si>
-  <si>
-    <t>1.09s</t>
-  </si>
-  <si>
-    <t>TC_SEC_030</t>
-  </si>
-  <si>
-    <t>TC_SEC_030 - Verify TLS version compliance checking</t>
-  </si>
-  <si>
-    <t>5:44:36 PM</t>
-  </si>
-  <si>
-    <t>5:44:39 PM</t>
-  </si>
-  <si>
-    <t>8.50s</t>
-  </si>
-  <si>
-    <t>TC_SEC_031</t>
-  </si>
-  <si>
-    <t>TC_SEC_031 - Verify API request rate limiting on forgot password</t>
-  </si>
-  <si>
-    <t>5:44:44 PM</t>
-  </si>
-  <si>
-    <t>5:44:47 PM</t>
-  </si>
-  <si>
-    <t>1.12s</t>
-  </si>
-  <si>
-    <t>TC_SEC_032</t>
-  </si>
-  <si>
-    <t>TC_SEC_032 - Verify secure header Referrer-Policy is set correctly</t>
-  </si>
-  <si>
-    <t>5:44:52 PM</t>
-  </si>
-  <si>
-    <t>5:44:55 PM</t>
-  </si>
-  <si>
-    <t>0.84s</t>
-  </si>
-  <si>
-    <t>TC_SEC_033</t>
-  </si>
-  <si>
-    <t>TC_SEC_033 - Verify session cookie path restricts access to domain</t>
-  </si>
-  <si>
-    <t>5:45:00 PM</t>
-  </si>
-  <si>
-    <t>5:45:03 PM</t>
-  </si>
-  <si>
-    <t>1.30s</t>
-  </si>
-  <si>
-    <t>TC_SEC_034</t>
-  </si>
-  <si>
-    <t>TC_SEC_034 - Verify brute force lockout mechanism on login</t>
-  </si>
-  <si>
-    <t>5:45:08 PM</t>
-  </si>
-  <si>
-    <t>5:45:11 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_035</t>
-  </si>
-  <si>
-    <t>TC_SEC_035 - Verify encryption of sensitive user payload at rest</t>
-  </si>
-  <si>
-    <t>5:45:16 PM</t>
-  </si>
-  <si>
-    <t>5:45:19 PM</t>
-  </si>
-  <si>
-    <t>1.91s</t>
-  </si>
-  <si>
     <t>TC_SEC_036</t>
   </si>
   <si>
     <t>TC_SEC_036 - Verify sanitization of file names on file system upload</t>
   </si>
   <si>
-    <t>5:45:24 PM</t>
-  </si>
-  <si>
-    <t>5:45:27 PM</t>
-  </si>
-  <si>
-    <t>1.74s</t>
+    <t>6:06:59 PM</t>
+  </si>
+  <si>
+    <t>6:07:02 PM</t>
+  </si>
+  <si>
+    <t>0.95s</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -665,7 +662,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T12:15:32.241Z</t>
+    <t>2026-06-15T12:37:07.309Z</t>
   </si>
   <si>
     <t>Execution of TC_SEC_001</t>
@@ -2054,7 +2051,7 @@
         <v>155</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -2080,70 +2077,70 @@
         <v>159</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>160</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="H30" s="2" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -2152,169 +2149,169 @@
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="H33" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="H34" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="G36" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="H36" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="G37" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="H37" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2338,13 +2335,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>207</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>17</v>
@@ -2353,18 +2350,18 @@
         <v>2</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>209</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>210</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>10</v>
@@ -2373,7 +2370,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2396,631 +2393,631 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>106</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>121</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>137</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>142</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>147</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>156</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="E31" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3042,70 +3039,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
